--- a/data/trans_dic/P04D$aparatos-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P04D$aparatos-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, tiene aparatos de calefacción en su vivienda</t>
+          <t>Población que, al menos, tiene aparatos de calefacción en su vivienda (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>64,74; 72,08</t>
+          <t>65,21; 72,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>50,49; 58,02</t>
+          <t>50,6; 58,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70,7; 78,92</t>
+          <t>70,66; 78,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65,38; 72,48</t>
+          <t>65,29; 72,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>51,6; 59,5</t>
+          <t>51,77; 59,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,16; 80,0</t>
+          <t>71,15; 79,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,36; 71,32</t>
+          <t>66,34; 71,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>52,34; 57,72</t>
+          <t>52,22; 57,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>72,46; 78,25</t>
+          <t>72,26; 77,96</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>63,0; 69,1</t>
+          <t>63,09; 69,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>53,49; 60,06</t>
+          <t>53,52; 60,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27,25; 65,21</t>
+          <t>23,17; 65,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65,49; 71,0</t>
+          <t>64,93; 71,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>53,47; 60,11</t>
+          <t>53,66; 60,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,18; 71,31</t>
+          <t>66,42; 71,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,01; 69,46</t>
+          <t>65,19; 69,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>54,43; 59,02</t>
+          <t>54,42; 59,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>39,65; 67,02</t>
+          <t>38,52; 67,18</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>62,98; 70,59</t>
+          <t>63,03; 70,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>38,91; 46,75</t>
+          <t>39,27; 46,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>60,67; 68,59</t>
+          <t>61,24; 69,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>68,76; 75,3</t>
+          <t>68,93; 75,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>37,49; 44,86</t>
+          <t>37,67; 44,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>65,46; 86,49</t>
+          <t>65,6; 86,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>66,89; 71,78</t>
+          <t>67,01; 71,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39,57; 44,83</t>
+          <t>39,59; 45,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>64,87; 80,9</t>
+          <t>64,88; 81,98</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>49,62; 56,53</t>
+          <t>50,07; 56,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>53,07; 59,57</t>
+          <t>53,19; 59,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52,31; 59,43</t>
+          <t>51,99; 59,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50,99; 57,01</t>
+          <t>50,8; 56,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50,86; 57,47</t>
+          <t>50,67; 57,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,79; 58,25</t>
+          <t>43,36; 58,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,3; 56,11</t>
+          <t>51,57; 56,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>52,97; 57,5</t>
+          <t>52,91; 57,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>48,35; 57,71</t>
+          <t>48,68; 57,98</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>61,54; 64,9</t>
+          <t>61,53; 64,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>51,2; 54,69</t>
+          <t>51,3; 54,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45,25; 64,75</t>
+          <t>46,61; 64,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63,32; 66,68</t>
+          <t>63,38; 66,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>50,72; 53,94</t>
+          <t>50,48; 53,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>62,9; 72,14</t>
+          <t>63,16; 72,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,96; 65,36</t>
+          <t>62,94; 65,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>51,46; 53,81</t>
+          <t>51,47; 53,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>56,47; 66,81</t>
+          <t>55,51; 66,86</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, tiene aparatos de calefacción en su vivienda</t>
+          <t>Población que, al menos, tiene aparatos de calefacción en su vivienda (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>453663; 505079</t>
+          <t>456935; 505052</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>340734; 391533</t>
+          <t>341424; 392956</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>447819; 499888</t>
+          <t>447560; 499714</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>455001; 504434</t>
+          <t>454358; 506555</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>347192; 400328</t>
+          <t>348335; 399230</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>515695; 579768</t>
+          <t>515649; 577886</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>926848; 996061</t>
+          <t>926495; 995012</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>705409; 777846</t>
+          <t>703775; 777360</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>984006; 1062750</t>
+          <t>981302; 1058754</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>639145; 701052</t>
+          <t>640038; 702082</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>546854; 614087</t>
+          <t>547247; 613713</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>324759; 777153</t>
+          <t>276119; 776659</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>674606; 731411</t>
+          <t>668838; 731756</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>557668; 626887</t>
+          <t>559630; 627793</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>632901; 681954</t>
+          <t>635246; 686493</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1329220; 1420247</t>
+          <t>1332836; 1420802</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1124112; 1218893</t>
+          <t>1123973; 1220698</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>851744; 1439605</t>
+          <t>827459; 1443252</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>476592; 534147</t>
+          <t>476954; 531972</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>295562; 355067</t>
+          <t>298297; 351872</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>426904; 482617</t>
+          <t>430890; 486101</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>533686; 584458</t>
+          <t>535024; 585855</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>294275; 352163</t>
+          <t>295737; 352006</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>609740; 805547</t>
+          <t>610994; 806780</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1025297; 1100350</t>
+          <t>1027207; 1102251</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>611157; 692484</t>
+          <t>611505; 696488</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1060719; 1322795</t>
+          <t>1060899; 1340357</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>470261; 535729</t>
+          <t>474538; 534618</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>497560; 558538</t>
+          <t>498689; 557323</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>483710; 549554</t>
+          <t>480760; 546358</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>536314; 599680</t>
+          <t>534351; 598518</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>530862; 599813</t>
+          <t>528911; 598806</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>467214; 636019</t>
+          <t>473509; 637291</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1025854; 1121901</t>
+          <t>1031255; 1122764</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1049526; 1139253</t>
+          <t>1048233; 1142084</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>975088; 1163908</t>
+          <t>981758; 1169347</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2104605; 2219363</t>
+          <t>2104221; 2220822</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1737791; 1856233</t>
+          <t>1741456; 1860158</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1562695; 2236086</t>
+          <t>1609846; 2234310</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2250375; 2369772</t>
+          <t>2252736; 2368984</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1797706; 1912004</t>
+          <t>1789234; 1913164</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2330217; 2672409</t>
+          <t>2339580; 2679549</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4390928; 4557754</t>
+          <t>4389541; 4560390</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3570685; 3733500</t>
+          <t>3571319; 3737823</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4041784; 4782236</t>
+          <t>3973335; 4786039</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P04D$aparatos-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P04D$aparatos-Habitat-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>73,79%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>65,21; 72,08</t>
+          <t>64,7; 71,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>50,6; 58,23</t>
+          <t>50,32; 58,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70,66; 78,89</t>
+          <t>70,81; 78,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65,29; 72,79</t>
+          <t>65,51; 72,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>51,77; 59,34</t>
+          <t>51,47; 59,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,15; 79,74</t>
+          <t>69,82; 75,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,34; 71,24</t>
+          <t>66,33; 71,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>52,22; 57,68</t>
+          <t>52,31; 57,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>72,26; 77,96</t>
+          <t>71,46; 76,1</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>67,07%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>63,09; 69,2</t>
+          <t>62,6; 69,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>53,52; 60,02</t>
+          <t>53,95; 59,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,17; 65,16</t>
+          <t>61,39; 68,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64,93; 71,04</t>
+          <t>65,44; 71,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>53,66; 60,2</t>
+          <t>53,26; 59,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,42; 71,78</t>
+          <t>66,76; 71,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,19; 69,49</t>
+          <t>64,86; 69,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>54,42; 59,1</t>
+          <t>54,3; 58,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>38,52; 67,18</t>
+          <t>64,71; 69,11</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>62,98%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>63,03; 70,3</t>
+          <t>63,15; 70,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39,27; 46,33</t>
+          <t>39,0; 46,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61,24; 69,08</t>
+          <t>58,82; 66,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>68,93; 75,48</t>
+          <t>68,48; 75,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>37,67; 44,84</t>
+          <t>37,88; 45,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>65,6; 86,62</t>
+          <t>60,24; 66,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>67,01; 71,91</t>
+          <t>66,75; 71,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39,59; 45,09</t>
+          <t>39,68; 44,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>64,88; 81,98</t>
+          <t>60,52; 65,57</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>56,78%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>50,07; 56,41</t>
+          <t>50,05; 56,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>53,19; 59,44</t>
+          <t>53,09; 59,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51,99; 59,08</t>
+          <t>52,96; 60,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50,8; 56,9</t>
+          <t>50,66; 57,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50,67; 57,37</t>
+          <t>51,18; 57,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,36; 58,36</t>
+          <t>54,07; 59,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,57; 56,15</t>
+          <t>51,29; 55,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>52,91; 57,64</t>
+          <t>52,74; 57,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>48,68; 57,98</t>
+          <t>54,69; 58,91</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>64,49%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>61,53; 64,94</t>
+          <t>61,28; 64,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>51,3; 54,8</t>
+          <t>51,34; 54,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46,61; 64,69</t>
+          <t>62,23; 65,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63,38; 66,65</t>
+          <t>63,42; 66,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>50,48; 53,97</t>
+          <t>50,55; 54,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,16; 72,33</t>
+          <t>63,58; 66,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,94; 65,39</t>
+          <t>62,95; 65,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>51,47; 53,87</t>
+          <t>51,39; 53,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>55,51; 66,86</t>
+          <t>63,44; 65,68</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>476371</t>
+          <t>514473</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>540264</t>
+          <t>534808</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1016635</t>
+          <t>1049281</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>456935; 505052</t>
+          <t>453322; 504085</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>341424; 392956</t>
+          <t>339562; 392247</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>447560; 499714</t>
+          <t>487540; 540061</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>454358; 506555</t>
+          <t>455923; 505634</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>348335; 399230</t>
+          <t>346331; 400247</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>515649; 577886</t>
+          <t>512157; 556773</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>926495; 995012</t>
+          <t>926317; 996904</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>703775; 777360</t>
+          <t>704897; 777416</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>981302; 1058754</t>
+          <t>1016181; 1082115</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>607653</t>
+          <t>676812</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>660405</t>
+          <t>742138</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1268057</t>
+          <t>1418950</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>640038; 702082</t>
+          <t>635139; 700682</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>547247; 613713</t>
+          <t>551565; 610039</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>276119; 776659</t>
+          <t>643189; 717019</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>668838; 731756</t>
+          <t>674062; 734142</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>559630; 627793</t>
+          <t>555447; 619650</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>635246; 686493</t>
+          <t>713008; 767552</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1332836; 1420802</t>
+          <t>1326213; 1416196</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1123973; 1220698</t>
+          <t>1121530; 1217736</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>827459; 1443252</t>
+          <t>1369026; 1462177</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>457039</t>
+          <t>501185</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>690650</t>
+          <t>511529</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1147689</t>
+          <t>1012715</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>476954; 531972</t>
+          <t>477875; 533041</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>298297; 351872</t>
+          <t>296195; 352889</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>430890; 486101</t>
+          <t>469217; 531181</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>535024; 585855</t>
+          <t>531501; 584868</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>295737; 352006</t>
+          <t>297356; 354435</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>610994; 806780</t>
+          <t>487999; 536690</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1027207; 1102251</t>
+          <t>1023208; 1100293</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>611505; 696488</t>
+          <t>612936; 694321</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1060899; 1340357</t>
+          <t>973052; 1054344</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>517857</t>
+          <t>559963</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>586344</t>
+          <t>634723</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1104201</t>
+          <t>1194686</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>474538; 534618</t>
+          <t>474346; 536921</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>498689; 557323</t>
+          <t>497734; 562079</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>480760; 546358</t>
+          <t>523230; 592873</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>534351; 598518</t>
+          <t>532869; 601845</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>528911; 598806</t>
+          <t>534198; 600048</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>473509; 637291</t>
+          <t>603466; 661180</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1031255; 1122764</t>
+          <t>1025524; 1115335</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1048233; 1142084</t>
+          <t>1045001; 1137933</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>981758; 1169347</t>
+          <t>1150547; 1239354</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2058920</t>
+          <t>2252433</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2477662</t>
+          <t>2423199</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4536582</t>
+          <t>4675633</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2104221; 2220822</t>
+          <t>2095498; 2220617</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1741456; 1860158</t>
+          <t>1742589; 1859574</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1609846; 2234310</t>
+          <t>2191626; 2316949</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2252736; 2368984</t>
+          <t>2254162; 2370938</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1789234; 1913164</t>
+          <t>1791631; 1914126</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2339580; 2679549</t>
+          <t>2370189; 2474243</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4389541; 4560390</t>
+          <t>4389925; 4545185</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3571319; 3737823</t>
+          <t>3566002; 3733767</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3973335; 4786039</t>
+          <t>4598997; 4761793</t>
         </is>
       </c>
     </row>
